--- a/results/ortools_stress_results.xlsx
+++ b/results/ortools_stress_results.xlsx
@@ -557,7 +557,7 @@
         <v>83.33</v>
       </c>
       <c r="N2" t="n">
-        <v>0.106</v>
+        <v>0.057</v>
       </c>
       <c r="O2" t="n">
         <v>168000</v>
@@ -613,7 +613,7 @@
         <v>100</v>
       </c>
       <c r="N3" t="n">
-        <v>0.345</v>
+        <v>0.354</v>
       </c>
       <c r="O3" t="n">
         <v>462000</v>
@@ -669,7 +669,7 @@
         <v>99.20999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>1.007</v>
+        <v>0.947</v>
       </c>
       <c r="O4" t="n">
         <v>1004000</v>
@@ -725,7 +725,7 @@
         <v>70.62</v>
       </c>
       <c r="N5" t="n">
-        <v>15.082</v>
+        <v>15.076</v>
       </c>
       <c r="O5" t="n">
         <v>1341000</v>
@@ -763,7 +763,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>16.843</v>
+        <v>20.164</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
